--- a/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 14,8</t>
+          <t>-15,91; 13,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 10,03</t>
+          <t>-11,09; 9,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 16,36</t>
+          <t>-13,9; 16,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 18,49</t>
+          <t>-20,08; 19,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 26,5</t>
+          <t>-22,36; 23,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 12,36</t>
+          <t>-12,05; 11,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 23,68</t>
+          <t>-16,89; 23,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 58,68</t>
+          <t>-44,15; 63,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 4,76</t>
+          <t>-6,73; 5,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,36</t>
+          <t>-1,27; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 5,12</t>
+          <t>-6,1; 5,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 1,72</t>
+          <t>-12,28; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 7,23</t>
+          <t>-9,55; 7,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,93</t>
+          <t>-1,41; 8,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 7,36</t>
+          <t>-7,96; 7,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 5,27</t>
+          <t>-31,57; 4,85</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 15,05</t>
+          <t>-2,13; 14,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 5,02</t>
+          <t>-5,0; 4,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,3; -1,49</t>
+          <t>-18,18; -1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 6,41</t>
+          <t>-8,3; 7,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 22,58</t>
+          <t>-2,81; 21,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,44</t>
+          <t>-5,25; 5,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -1,77</t>
+          <t>-21,28; -1,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 31,67</t>
+          <t>-28,8; 37,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,57</t>
+          <t>-3,89; 5,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,38</t>
+          <t>-1,04; 5,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,97</t>
+          <t>-6,77; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 2,12</t>
+          <t>-8,46; 1,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,48</t>
+          <t>-5,51; 7,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,26</t>
+          <t>-1,15; 5,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,65</t>
+          <t>-8,81; 2,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,16; 7,14</t>
+          <t>-25,19; 5,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 13,14</t>
+          <t>-16,6; 12,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 9,59</t>
+          <t>-10,61; 10,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 16,03</t>
+          <t>-14,38; 14,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 19,41</t>
+          <t>-21,16; 19,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 23,02</t>
+          <t>-23,03; 22,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 11,97</t>
+          <t>-11,64; 12,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 23,05</t>
+          <t>-17,51; 20,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 63,79</t>
+          <t>-47,45; 58,75</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,0</t>
+          <t>-7,03; 5,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,4</t>
+          <t>-0,96; 7,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 5,22</t>
+          <t>-6,03; 4,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 1,68</t>
+          <t>-11,91; 2,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 7,68</t>
+          <t>-10,08; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,86</t>
+          <t>-1,06; 8,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 7,52</t>
+          <t>-7,94; 6,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 4,85</t>
+          <t>-31,27; 6,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 14,89</t>
+          <t>-3,06; 14,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,92</t>
+          <t>-4,92; 4,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -1,31</t>
+          <t>-17,62; -1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 7,66</t>
+          <t>-9,33; 7,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 21,9</t>
+          <t>-3,97; 21,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 5,34</t>
+          <t>-5,19; 5,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,28; -1,68</t>
+          <t>-21,15; -2,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 37,87</t>
+          <t>-32,91; 36,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,29</t>
+          <t>-4,02; 5,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,12</t>
+          <t>-1,18; 5,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,68</t>
+          <t>-6,67; 1,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 1,74</t>
+          <t>-8,22; 1,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,88</t>
+          <t>-5,65; 8,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,97</t>
+          <t>-1,35; 6,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,28</t>
+          <t>-8,56; 2,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 5,52</t>
+          <t>-23,61; 5,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,66</t>
+          <t>-5,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,66%</t>
+          <t>-14,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 12,39</t>
+          <t>-14,69; 14,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 10,34</t>
+          <t>-10,52; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 14,94</t>
+          <t>-12,67; 16,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 19,61</t>
+          <t>-20,59; 9,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 22,42</t>
+          <t>-21,39; 26,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 12,68</t>
+          <t>-11,52; 12,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 20,79</t>
+          <t>-16,07; 23,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 58,75</t>
+          <t>-43,99; 29,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-2,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-12,23%</t>
+          <t>-7,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 5,45</t>
+          <t>-6,85; 4,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 7,52</t>
+          <t>-0,85; 7,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 4,72</t>
+          <t>-5,83; 5,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 2,05</t>
+          <t>-8,65; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 8,39</t>
+          <t>-9,85; 7,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 8,96</t>
+          <t>-0,96; 8,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 6,7</t>
+          <t>-7,64; 7,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 6,69</t>
+          <t>-22,39; 8,58</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>-8,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 14,74</t>
+          <t>-2,62; 15,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,93</t>
+          <t>-4,47; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,62; -1,91</t>
+          <t>-18,3; -1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 7,33</t>
+          <t>-10,68; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 21,9</t>
+          <t>-3,4; 22,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 5,39</t>
+          <t>-4,64; 5,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -2,53</t>
+          <t>-21,09; -1,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 36,25</t>
+          <t>-36,41; 26,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,69%</t>
+          <t>-8,5%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,44</t>
+          <t>-3,58; 5,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,29</t>
+          <t>-1,15; 5,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,69</t>
+          <t>-6,82; 1,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 1,95</t>
+          <t>-7,77; 1,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,22</t>
+          <t>-5,07; 8,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,15</t>
+          <t>-1,3; 6,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 2,29</t>
+          <t>-8,78; 2,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 5,98</t>
+          <t>-21,39; 5,67</t>
         </is>
       </c>
     </row>
